--- a/01_Accounting_System/مستندات_المشتريات_والموردين/سجل_أوامر_الشراء_حسب_الموردين.xlsx
+++ b/01_Accounting_System/مستندات_المشتريات_والموردين/سجل_أوامر_الشراء_حسب_الموردين.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="59">
   <si>
     <t>🛒 فندق هينو الأهرامات — سجل ودليل أوامر الشراء الكودية المسلسلة حسب الموردين (Vendor PO Log)</t>
   </si>
@@ -73,6 +73,36 @@
     <t>نقداً عند التسليم</t>
   </si>
   <si>
+    <t>QN_3</t>
+  </si>
+  <si>
+    <t>أمر توريد مفروشات وبياضات شركة كوين v3 (سابق)</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>35,400 جـ</t>
+  </si>
+  <si>
+    <t>مستند توريد سابق معتمد</t>
+  </si>
+  <si>
+    <t>مستند سابق معتمد 🟢</t>
+  </si>
+  <si>
+    <t>QN_4</t>
+  </si>
+  <si>
+    <t>أمر توريد مفروشات شركة كوين جديد (سابق)</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>42,000 جـ</t>
+  </si>
+  <si>
     <t>AH_1</t>
   </si>
   <si>
@@ -115,9 +145,6 @@
     <t>أمر شراء وتوريد لمبات ليد ومستلزمات إضاءة الغرف</t>
   </si>
   <si>
-    <t>2026-08-05</t>
-  </si>
-  <si>
     <t>11,350 جـ</t>
   </si>
   <si>
@@ -139,7 +166,7 @@
     <t>CF_1</t>
   </si>
   <si>
-    <t>شركة كير فرش لمواد ومساحيق النظافة والتطوير</t>
+    <t>شركة كير فرش لمواد ومساحيق النظافة</t>
   </si>
   <si>
     <t>أمر شراء وتوريد المنظفات ومطهرات الأرضيات والحمامات</t>
@@ -154,13 +181,10 @@
     <t>FR_1</t>
   </si>
   <si>
-    <t>مورد الفرسان لقطع غيار السباكة والتكييف والصيانة</t>
+    <t>مورد الفرسان لقطع غيار السباكة والتكييف</t>
   </si>
   <si>
     <t>أمر شراء وتوريد قطع غيار السباكة والتكييفات</t>
-  </si>
-  <si>
-    <t>2026-08-11</t>
   </si>
   <si>
     <t>6,040 جـ</t>
@@ -600,12 +624,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="24" customWidth="1"/>
@@ -697,22 +721,22 @@
         <v>20</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -720,7 +744,7 @@
         <v>26</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>27</v>
@@ -732,30 +756,30 @@
         <v>29</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>14</v>
@@ -763,22 +787,22 @@
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>14</v>
@@ -795,13 +819,13 @@
         <v>43</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>14</v>
@@ -812,21 +836,67 @@
         <v>46</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="B12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>14</v>
       </c>
     </row>

--- a/01_Accounting_System/مستندات_المشتريات_والموردين/سجل_أوامر_الشراء_حسب_الموردين.xlsx
+++ b/01_Accounting_System/مستندات_المشتريات_والموردين/سجل_أوامر_الشراء_حسب_الموردين.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="56">
   <si>
     <t>🛒 فندق هينو الأهرامات — سجل ودليل أوامر الشراء الكودية المسلسلة حسب الموردين (Vendor PO Log)</t>
   </si>
@@ -76,115 +76,106 @@
     <t>QN_3</t>
   </si>
   <si>
-    <t>أمر توريد مفروشات وبياضات شركة كوين v3 (سابق)</t>
+    <t>أمر شراء وتوريد لحف فندقية وكفرات لحاف فردي وكبير</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>36,400 جـ</t>
+  </si>
+  <si>
+    <t>تم الاعتماد جاري التوريد 🟢</t>
+  </si>
+  <si>
+    <t>AH_1</t>
+  </si>
+  <si>
+    <t>شركة الأهرام لخدمات ومستلزمات الضيافة</t>
+  </si>
+  <si>
+    <t>أمر شراء وتوريد مستلزمات ضيافة النزلاء (Amenities)</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>22,500 جـ</t>
+  </si>
+  <si>
+    <t>آجل 15 يوماً</t>
+  </si>
+  <si>
+    <t>AH_2</t>
+  </si>
+  <si>
+    <t>أمر شراء وتوريد أكواب ومستلزمات الكيتل والغرف</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>9,100 جـ</t>
+  </si>
+  <si>
+    <t>نقداً عند الاستلام</t>
+  </si>
+  <si>
+    <t>NR_1</t>
+  </si>
+  <si>
+    <t>مورد النور للتجهيزات ومستلزمات الكهرباء</t>
+  </si>
+  <si>
+    <t>أمر شراء وتوريد لمبات ليد ومستلزمات إضاءة الغرف</t>
   </si>
   <si>
     <t>2026-08-05</t>
   </si>
   <si>
-    <t>35,400 جـ</t>
-  </si>
-  <si>
-    <t>مستند توريد سابق معتمد</t>
-  </si>
-  <si>
-    <t>مستند سابق معتمد 🟢</t>
-  </si>
-  <si>
-    <t>QN_4</t>
-  </si>
-  <si>
-    <t>أمر توريد مفروشات شركة كوين جديد (سابق)</t>
+    <t>11,350 جـ</t>
+  </si>
+  <si>
+    <t>نقداً كاش</t>
+  </si>
+  <si>
+    <t>NR_2</t>
+  </si>
+  <si>
+    <t>أمر شراء وتوريد بطاريات ريموت ووصلات شاشات</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>2,775 جـ</t>
+  </si>
+  <si>
+    <t>CF_1</t>
+  </si>
+  <si>
+    <t>شركة كير فرش لمواد ومساحيق النظافة</t>
+  </si>
+  <si>
+    <t>أمر شراء وتوريد المنظفات ومطهرات الأرضيات والحمامات</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>7,860 جـ</t>
+  </si>
+  <si>
+    <t>FR_1</t>
+  </si>
+  <si>
+    <t>مورد الفرسان لقطع غيار السباكة والتكييف</t>
+  </si>
+  <si>
+    <t>أمر شراء وتوريد قطع غيار السباكة والتكييفات</t>
   </si>
   <si>
     <t>2026-08-11</t>
-  </si>
-  <si>
-    <t>42,000 جـ</t>
-  </si>
-  <si>
-    <t>AH_1</t>
-  </si>
-  <si>
-    <t>شركة الأهرام لخدمات ومستلزمات الضيافة</t>
-  </si>
-  <si>
-    <t>أمر شراء وتوريد مستلزمات ضيافة النزلاء (Amenities)</t>
-  </si>
-  <si>
-    <t>2026-08-03</t>
-  </si>
-  <si>
-    <t>22,500 جـ</t>
-  </si>
-  <si>
-    <t>آجل 15 يوماً</t>
-  </si>
-  <si>
-    <t>AH_2</t>
-  </si>
-  <si>
-    <t>أمر شراء وتوريد أكواب ومستلزمات الكيتل والغرف</t>
-  </si>
-  <si>
-    <t>2026-08-12</t>
-  </si>
-  <si>
-    <t>9,100 جـ</t>
-  </si>
-  <si>
-    <t>نقداً عند الاستلام</t>
-  </si>
-  <si>
-    <t>NR_1</t>
-  </si>
-  <si>
-    <t>مورد النور للتجهيزات ومستلزمات الكهرباء</t>
-  </si>
-  <si>
-    <t>أمر شراء وتوريد لمبات ليد ومستلزمات إضاءة الغرف</t>
-  </si>
-  <si>
-    <t>11,350 جـ</t>
-  </si>
-  <si>
-    <t>نقداً كاش</t>
-  </si>
-  <si>
-    <t>NR_2</t>
-  </si>
-  <si>
-    <t>أمر شراء وتوريد بطاريات ريموت ووصلات شاشات</t>
-  </si>
-  <si>
-    <t>2026-08-14</t>
-  </si>
-  <si>
-    <t>2,775 جـ</t>
-  </si>
-  <si>
-    <t>CF_1</t>
-  </si>
-  <si>
-    <t>شركة كير فرش لمواد ومساحيق النظافة</t>
-  </si>
-  <si>
-    <t>أمر شراء وتوريد المنظفات ومطهرات الأرضيات والحمامات</t>
-  </si>
-  <si>
-    <t>2026-08-08</t>
-  </si>
-  <si>
-    <t>7,860 جـ</t>
-  </si>
-  <si>
-    <t>FR_1</t>
-  </si>
-  <si>
-    <t>مورد الفرسان لقطع غيار السباكة والتكييف</t>
-  </si>
-  <si>
-    <t>أمر شراء وتوريد قطع غيار السباكة والتكييفات</t>
   </si>
   <si>
     <t>6,040 جـ</t>
@@ -624,12 +615,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="24" customWidth="1"/>
@@ -733,18 +724,18 @@
         <v>23</v>
       </c>
       <c r="F6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>9</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>27</v>
@@ -756,18 +747,18 @@
         <v>29</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>32</v>
@@ -790,19 +781,19 @@
         <v>36</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>14</v>
@@ -810,22 +801,22 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>43</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>14</v>
@@ -836,19 +827,19 @@
         <v>46</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>14</v>
@@ -856,47 +847,24 @@
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="3" t="s">
         <v>14</v>
       </c>
     </row>
